--- a/stick-world/config/excel/制造.xlsx
+++ b/stick-world/config/excel/制造.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="制造" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="manufacturing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -455,119 +455,93 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>prerequisites</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>research_cost</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unlocks</t>
+          <t>#output_dir: manufacturing</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>层级</t>
+          <t>tier</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>category</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>前置科技</t>
+          <t>prerequisites</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>研究消耗</t>
+          <t>research_cost</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>解锁内容</t>
+          <t>unlocks</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tech_stone_tools</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>石器工具</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>层级</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>economy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>前置科技</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>研究消耗</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["stone_axe","stone_pickaxe","basic_quarry"]</t>
+          <t>解锁内容</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tech_basic_combat</t>
+          <t>tech_stone_tools</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>基础战斗</t>
+          <t>石器工具</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -577,30 +551,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>military</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>economy</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["warrior","spear","wooden_shield"]</t>
+          <t>["stone_axe","stone_pickaxe","basic_quarry"]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tech_primitive_administration</t>
+          <t>tech_basic_combat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>原始行政管理</t>
+          <t>基础战斗</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -610,67 +583,61 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>administration</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>military</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["tribal_council","basic_laws","census_tent"]</t>
+          <t>["warrior","spear","wooden_shield"]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tech_bronze_working</t>
+          <t>tech_primitive_administration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>青铜冶炼</t>
+          <t>原始行政管理</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>economy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>tech_stone_tools</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["bronze_axe","bronze_pickaxe","smelter","copper_mine"]</t>
+          <t>["tribal_council","basic_laws","census_tent"]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tech_formation_tactics</t>
+          <t>tech_bronze_working</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>阵型战术</t>
+          <t>青铜冶炼</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -680,34 +647,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>military</t>
+          <t>economy</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tech_basic_combat</t>
+          <t>tech_stone_tools</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["spearman","shield_wall","barracks","military_drill"]</t>
+          <t>["bronze_axe","bronze_pickaxe","smelter","copper_mine"]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tech_early_writing</t>
+          <t>tech_formation_tactics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>早期文字</t>
+          <t>阵型战术</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -717,34 +684,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>military</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tech_primitive_administration</t>
+          <t>tech_basic_combat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["scribe","clay_tablet","record_keeping","royal_decree"]</t>
+          <t>["spearman","shield_wall","barracks","military_drill"]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tech_herbal_medicine</t>
+          <t>tech_early_writing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>草药医学</t>
+          <t>早期文字</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -754,7 +721,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>science</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -764,61 +731,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["herbalist","field_hospital","healing_salve"]</t>
+          <t>["scribe","clay_tablet","record_keeping","royal_decree"]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tech_iron_working</t>
+          <t>tech_herbal_medicine</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>铁器锻造</t>
+          <t>草药医学</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>science</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tech_bronze_working</t>
+          <t>tech_primitive_administration</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>280</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["iron_axe","iron_pickaxe","blast_furnace","iron_mine"]</t>
+          <t>["herbalist","field_hospital","healing_salve"]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tech_cavalry_warfare</t>
+          <t>tech_iron_working</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>骑兵战术</t>
+          <t>铁器锻造</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -828,34 +795,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>military</t>
+          <t>economy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tech_formation_tactics,tech_bronze_working</t>
+          <t>tech_bronze_working</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["horseman","cavalry_archer","stable","horse_breeding"]</t>
+          <t>["iron_axe","iron_pickaxe","blast_furnace","iron_mine"]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tech_philosophy</t>
+          <t>tech_cavalry_warfare</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>哲学思想</t>
+          <t>骑兵战术</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -865,34 +832,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>science</t>
+          <t>military</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tech_early_writing,tech_herbal_medicine</t>
+          <t>tech_formation_tactics,tech_bronze_working</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["philosopher","academy","natural_philosophy","logic"]</t>
+          <t>["horseman","cavalry_archer","stable","horse_breeding"]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tech_bureaucracy</t>
+          <t>tech_philosophy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>官僚制度</t>
+          <t>哲学思想</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -902,57 +869,94 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>science</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tech_early_writing</t>
+          <t>tech_early_writing,tech_herbal_medicine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>550</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["bureaucrat","tax_office","census","archives"]</t>
+          <t>["philosopher","academy","natural_philosophy","logic"]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>tech_bureaucracy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>官僚制度</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tech_early_writing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>["bureaucrat","tax_office","census","archives"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>tech_trade_networks</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>贸易网络</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>tech_early_writing,tech_bronze_working</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>["merchant","marketplace","trade_route","currency"]</t>
         </is>
